--- a/copilot/examples/02_summary_and_total_row.xlsx
+++ b/copilot/examples/02_summary_and_total_row.xlsx
@@ -1045,17 +1045,19 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What Copilot gives with files 11 and 12 loaded: the map, then a query per final. Fill in &lt;database&gt; with your database's name. Delete this sheet before you try the workbook on Copilot yourself.</t>
-        </is>
-      </c>
-    </row>
+          <t>What Copilot gives with files 11, 12, 03, 04 and 05 loaded: the map, then a query per final. Fill in &lt;database&gt; with your database's name. Delete this sheet, and the Power Query sheet if there is one, before you try the workbook on Copilot yourself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Sources: job_runs. Finals: by_job (job_id, total_mins, runs, failed, longest), a summary: a GROUP BY of job_runs. Its Total Row adds up sums and counts and takes the MAX of the MAXes, so it is the summary's WITH ROLLUP row, its job_id NULL. Fill in: &lt;database&gt;.</t>
-        </is>
-      </c>
-    </row>
+          <t>Sources: job_runs. Finals: by_job (job_id, total_mins, runs, failed, longest), a summary: a GROUP BY of job_runs. Its Total Row adds up sums and counts and takes the MAX of the MAXes, so it is the Subtotal row WITH ROLLUP adds, its job_id NULL. Fill in: &lt;database&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>

--- a/copilot/examples/02_summary_and_total_row.xlsx
+++ b/copilot/examples/02_summary_and_total_row.xlsx
@@ -193,13 +193,13 @@
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="by_job" displayName="by_job" ref="A1:E5" headerRowCount="1" totalsRowCount="1">
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E4"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="job_id"/>
-    <tableColumn id="2" name="total_mins"/>
-    <tableColumn id="3" name="runs"/>
-    <tableColumn id="4" name="failed"/>
-    <tableColumn id="5" name="longest"/>
+    <tableColumn id="1" name="job_id" totalsRowLabel="Total"/>
+    <tableColumn id="2" name="total_mins" totalsRowFunction="sum"/>
+    <tableColumn id="3" name="runs" totalsRowFunction="sum"/>
+    <tableColumn id="4" name="failed" totalsRowFunction="sum"/>
+    <tableColumn id="5" name="longest" totalsRowFunction="max"/>
   </tableColumns>
 </table>
 </file>
